--- a/pareto_cpius/data/raw/atlanta/stickyprice.xlsx
+++ b/pareto_cpius/data/raw/atlanta/stickyprice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\f1egm02\ATL FRB Dropbox\Emil Mihaylov\Pi_day\StickyCPI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8F7726-60E8-41D5-ACF4-5A96190EBB9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF462F11-CCAB-43B5-9555-DB557BFDE461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65870,31 +65870,81 @@
       </c>
     </row>
     <row r="718" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A718" s="23"/>
-      <c r="B718" s="28"/>
-      <c r="C718" s="27"/>
-      <c r="D718" s="27"/>
-      <c r="E718" s="27"/>
-      <c r="F718" s="28"/>
-      <c r="G718" s="27"/>
-      <c r="H718" s="27"/>
-      <c r="I718" s="27"/>
-      <c r="J718" s="28"/>
-      <c r="K718" s="27"/>
-      <c r="L718" s="27"/>
-      <c r="M718" s="27"/>
-      <c r="N718" s="28"/>
-      <c r="O718" s="27"/>
-      <c r="P718" s="27"/>
-      <c r="Q718" s="27"/>
-      <c r="R718" s="28"/>
-      <c r="S718" s="27"/>
-      <c r="T718" s="27"/>
-      <c r="U718" s="27"/>
-      <c r="V718" s="28"/>
-      <c r="W718" s="27"/>
-      <c r="X718" s="27"/>
-      <c r="Y718" s="27"/>
+      <c r="A718" s="23">
+        <v>46266</v>
+      </c>
+      <c r="B718" s="28">
+        <v>1.6861745309760954E-2</v>
+      </c>
+      <c r="C718" s="27">
+        <v>22.220178031362558</v>
+      </c>
+      <c r="D718" s="27">
+        <v>8.171584424086543</v>
+      </c>
+      <c r="E718" s="27">
+        <v>6.1232486883173287</v>
+      </c>
+      <c r="F718" s="28">
+        <v>6.3669445137352508E-3</v>
+      </c>
+      <c r="G718" s="27">
+        <v>7.9136445480548323</v>
+      </c>
+      <c r="H718" s="27">
+        <v>3.9118735782125436</v>
+      </c>
+      <c r="I718" s="27">
+        <v>1.4794865276949842</v>
+      </c>
+      <c r="J718" s="28">
+        <v>2.7911441331132177E-3</v>
+      </c>
+      <c r="K718" s="27">
+        <v>3.401271558305563</v>
+      </c>
+      <c r="L718" s="27">
+        <v>3.325498908348079</v>
+      </c>
+      <c r="M718" s="27">
+        <v>2.8155337303794603</v>
+      </c>
+      <c r="N718" s="28">
+        <v>2.864107380401919E-3</v>
+      </c>
+      <c r="O718" s="27">
+        <v>3.4915896168763227</v>
+      </c>
+      <c r="P718" s="27">
+        <v>3.3598935452550105</v>
+      </c>
+      <c r="Q718" s="27">
+        <v>2.7765285544586682</v>
+      </c>
+      <c r="R718" s="28">
+        <v>2.3934306902160234E-3</v>
+      </c>
+      <c r="S718" s="27">
+        <v>2.9102282654162481</v>
+      </c>
+      <c r="T718" s="27">
+        <v>3.5295654871302817</v>
+      </c>
+      <c r="U718" s="27">
+        <v>2.5057892993376241</v>
+      </c>
+      <c r="V718" s="28">
+        <v>2.4675559985346562E-3</v>
+      </c>
+      <c r="W718" s="27">
+        <v>3.0015858756434088</v>
+      </c>
+      <c r="X718" s="27">
+        <v>3.6379312789169838</v>
+      </c>
+      <c r="Y718" s="27">
+        <v>2.3618265730061871</v>
+      </c>
     </row>
     <row r="719" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A719" s="23"/>
